--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/79.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/79.xlsx
@@ -426,13 +426,13 @@
         <v>-3.881683751896816</v>
       </c>
       <c r="E2">
-        <v>-4.260675716986357</v>
+        <v>-3.536477625205706</v>
       </c>
       <c r="F2">
-        <v>-4.481662462732491</v>
+        <v>-4.400185901727937</v>
       </c>
       <c r="G2">
-        <v>-3.75265980407953</v>
+        <v>-4.622308203751638</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.387285194892391</v>
       </c>
       <c r="E3">
-        <v>-3.898307226892575</v>
+        <v>-5.490577558151573</v>
       </c>
       <c r="F3">
-        <v>-4.349143559102237</v>
+        <v>-4.03564957224757</v>
       </c>
       <c r="G3">
-        <v>-3.869530353583832</v>
+        <v>-4.839941786124927</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.094707355587815</v>
       </c>
       <c r="E4">
-        <v>-4.976622929125034</v>
+        <v>-6.205306610782185</v>
       </c>
       <c r="F4">
-        <v>-4.242532674361941</v>
+        <v>-4.044615821015472</v>
       </c>
       <c r="G4">
-        <v>-4.343840773666243</v>
+        <v>-4.879168789868089</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.061876241037474</v>
       </c>
       <c r="E5">
-        <v>-5.931030525559615</v>
+        <v>-6.141667965552394</v>
       </c>
       <c r="F5">
-        <v>-4.359029295687247</v>
+        <v>-3.963783729850296</v>
       </c>
       <c r="G5">
-        <v>-3.598711450953502</v>
+        <v>-4.720078762558412</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.221001647270826</v>
       </c>
       <c r="E6">
-        <v>-5.446366066414687</v>
+        <v>-6.670095597507448</v>
       </c>
       <c r="F6">
-        <v>-4.246523748508629</v>
+        <v>-4.057759526595691</v>
       </c>
       <c r="G6">
-        <v>-4.005746985402619</v>
+        <v>-4.720938442606987</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.509384866444453</v>
       </c>
       <c r="E7">
-        <v>-6.768499337694124</v>
+        <v>-8.586015966094646</v>
       </c>
       <c r="F7">
-        <v>-4.324004265162078</v>
+        <v>-3.853060829322503</v>
       </c>
       <c r="G7">
-        <v>-3.856165938172213</v>
+        <v>-4.229792074703064</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.839135938908714</v>
       </c>
       <c r="E8">
-        <v>-7.366651883945279</v>
+        <v>-9.079325282120216</v>
       </c>
       <c r="F8">
-        <v>-4.459558306956189</v>
+        <v>-3.688424464750907</v>
       </c>
       <c r="G8">
-        <v>-3.637173930073313</v>
+        <v>-5.328495988996889</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.126393497881248</v>
       </c>
       <c r="E9">
-        <v>-8.115376190951473</v>
+        <v>-9.471300935276147</v>
       </c>
       <c r="F9">
-        <v>-4.287135288798278</v>
+        <v>-4.40045594950125</v>
       </c>
       <c r="G9">
-        <v>-3.201847703338664</v>
+        <v>-5.359910404207013</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.291649552236143</v>
       </c>
       <c r="E10">
-        <v>-8.803577442845153</v>
+        <v>-9.646996669825741</v>
       </c>
       <c r="F10">
-        <v>-4.188461820511606</v>
+        <v>-3.924346814537817</v>
       </c>
       <c r="G10">
-        <v>-2.976221065246567</v>
+        <v>-3.957916618730594</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.276944428712145</v>
       </c>
       <c r="E11">
-        <v>-9.227320341164891</v>
+        <v>-11.41620806598644</v>
       </c>
       <c r="F11">
-        <v>-4.426072383065422</v>
+        <v>-4.266085644725739</v>
       </c>
       <c r="G11">
-        <v>-2.886286063523747</v>
+        <v>-3.976173335487344</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.044363277023239</v>
       </c>
       <c r="E12">
-        <v>-9.887250329828685</v>
+        <v>-10.55997778603816</v>
       </c>
       <c r="F12">
-        <v>-4.027522459658704</v>
+        <v>-3.834517825010836</v>
       </c>
       <c r="G12">
-        <v>-1.807184166826044</v>
+        <v>-3.854433453188826</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.581573382010617</v>
       </c>
       <c r="E13">
-        <v>-11.09977641622647</v>
+        <v>-12.21742644368955</v>
       </c>
       <c r="F13">
-        <v>-4.204611671396585</v>
+        <v>-3.894250570059306</v>
       </c>
       <c r="G13">
-        <v>-1.490326444495147</v>
+        <v>-3.098003603425358</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.906218029486244</v>
       </c>
       <c r="E14">
-        <v>-11.4321845222855</v>
+        <v>-12.9553186408694</v>
       </c>
       <c r="F14">
-        <v>-4.809090417669649</v>
+        <v>-4.045824409056157</v>
       </c>
       <c r="G14">
-        <v>-0.991590611124228</v>
+        <v>-1.172359669277156</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.062742209565154</v>
       </c>
       <c r="E15">
-        <v>-12.25975409023925</v>
+        <v>-13.117442538818</v>
       </c>
       <c r="F15">
-        <v>-4.393373408207314</v>
+        <v>-3.897745452131717</v>
       </c>
       <c r="G15">
-        <v>-0.01706452674758797</v>
+        <v>-1.946590146000613</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.118901764630313</v>
       </c>
       <c r="E16">
-        <v>-13.2921918223</v>
+        <v>-14.06249883642675</v>
       </c>
       <c r="F16">
-        <v>-4.149456484615985</v>
+        <v>-4.038972153900199</v>
       </c>
       <c r="G16">
-        <v>1.018840088120025</v>
+        <v>0.000660632116532384</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.1584767890606985</v>
       </c>
       <c r="E17">
-        <v>-13.45841851769955</v>
+        <v>-14.52755953159247</v>
       </c>
       <c r="F17">
-        <v>-4.256389604275971</v>
+        <v>-3.372380763030423</v>
       </c>
       <c r="G17">
-        <v>1.786626245700732</v>
+        <v>0.2033351254003136</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.7279244809956604</v>
       </c>
       <c r="E18">
-        <v>-14.33384499896635</v>
+        <v>-16.5073223267398</v>
       </c>
       <c r="F18">
-        <v>-3.954646837397418</v>
+        <v>-3.293725621399804</v>
       </c>
       <c r="G18">
-        <v>1.448584956982059</v>
+        <v>-0.02268854050047621</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.457717949361832</v>
       </c>
       <c r="E19">
-        <v>-14.96521843053778</v>
+        <v>-16.15301452037967</v>
       </c>
       <c r="F19">
-        <v>-3.730837704141644</v>
+        <v>-3.100652232257504</v>
       </c>
       <c r="G19">
-        <v>2.286907534426148</v>
+        <v>0.0869633215730473</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.967236632258655</v>
       </c>
       <c r="E20">
-        <v>-16.16996459859039</v>
+        <v>-17.42827355720572</v>
       </c>
       <c r="F20">
-        <v>-3.278554900784934</v>
+        <v>-3.008795399328469</v>
       </c>
       <c r="G20">
-        <v>2.508071711197401</v>
+        <v>0.8613217659373219</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.219693042445529</v>
       </c>
       <c r="E21">
-        <v>-17.34766219139518</v>
+        <v>-18.08762390119653</v>
       </c>
       <c r="F21">
-        <v>-3.073714552685867</v>
+        <v>-2.904236380644907</v>
       </c>
       <c r="G21">
-        <v>2.707468264143297</v>
+        <v>0.9529334718770184</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.209428151662144</v>
       </c>
       <c r="E22">
-        <v>-17.95810501610315</v>
+        <v>-19.12548674511847</v>
       </c>
       <c r="F22">
-        <v>-3.097450592245683</v>
+        <v>-2.621411868511489</v>
       </c>
       <c r="G22">
-        <v>2.726007165954159</v>
+        <v>0.5886325670181093</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.961983577217244</v>
       </c>
       <c r="E23">
-        <v>-18.16094895232873</v>
+        <v>-19.74582881400721</v>
       </c>
       <c r="F23">
-        <v>-2.801849341291486</v>
+        <v>-2.537028566290512</v>
       </c>
       <c r="G23">
-        <v>2.681940360410817</v>
+        <v>0.2350448505507873</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.529250937544132</v>
       </c>
       <c r="E24">
-        <v>-17.98802464387183</v>
+        <v>-19.56210862351602</v>
       </c>
       <c r="F24">
-        <v>-2.633775251998272</v>
+        <v>-2.378352305182058</v>
       </c>
       <c r="G24">
-        <v>2.126242520767938</v>
+        <v>0.1797989231544166</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.9802071589368438</v>
       </c>
       <c r="E25">
-        <v>-19.36284671023051</v>
+        <v>-19.51373546416609</v>
       </c>
       <c r="F25">
-        <v>-2.27249854824792</v>
+        <v>-1.766182167574001</v>
       </c>
       <c r="G25">
-        <v>1.739045251867224</v>
+        <v>0.01099648002878324</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.3918972497294001</v>
       </c>
       <c r="E26">
-        <v>-18.31731715981358</v>
+        <v>-20.28416021861704</v>
       </c>
       <c r="F26">
-        <v>-2.41803276051096</v>
+        <v>-1.951823444378384</v>
       </c>
       <c r="G26">
-        <v>1.776579145285712</v>
+        <v>-0.8063558104288955</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.1605927558034458</v>
       </c>
       <c r="E27">
-        <v>-19.09371497148065</v>
+        <v>-19.17526373141078</v>
       </c>
       <c r="F27">
-        <v>-2.205614507411083</v>
+        <v>-1.738974440229051</v>
       </c>
       <c r="G27">
-        <v>1.360562907428395</v>
+        <v>-0.9967749411881507</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.6120739183715935</v>
       </c>
       <c r="E28">
-        <v>-18.89328471190116</v>
+        <v>-20.96855302387026</v>
       </c>
       <c r="F28">
-        <v>-2.21942339201575</v>
+        <v>-1.394704947625577</v>
       </c>
       <c r="G28">
-        <v>1.012080771707569</v>
+        <v>-0.5812705738941069</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.9139706509305501</v>
       </c>
       <c r="E29">
-        <v>-18.57587038328152</v>
+        <v>-19.66975045067834</v>
       </c>
       <c r="F29">
-        <v>-2.122805103255424</v>
+        <v>-2.028130992789469</v>
       </c>
       <c r="G29">
-        <v>0.8312690576743678</v>
+        <v>-1.293978146377975</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.037183990690272</v>
       </c>
       <c r="E30">
-        <v>-18.60468506339233</v>
+        <v>-18.95568255525285</v>
       </c>
       <c r="F30">
-        <v>-2.056030406915756</v>
+        <v>-1.394021544518267</v>
       </c>
       <c r="G30">
-        <v>0.747624157681003</v>
+        <v>-1.36391082147442</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.9718599103225871</v>
       </c>
       <c r="E31">
-        <v>-18.16469852880708</v>
+        <v>-20.29650031028794</v>
       </c>
       <c r="F31">
-        <v>-2.267794249767422</v>
+        <v>-1.625463255023435</v>
       </c>
       <c r="G31">
-        <v>0.4748037098994127</v>
+        <v>-0.7303331881181209</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.7271026059268025</v>
       </c>
       <c r="E32">
-        <v>-17.91727176597599</v>
+        <v>-20.50254587763694</v>
       </c>
       <c r="F32">
-        <v>-1.917602758601334</v>
+        <v>-1.492868141592124</v>
       </c>
       <c r="G32">
-        <v>0.3407789340823338</v>
+        <v>-0.9054388578594476</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.3275366466201372</v>
       </c>
       <c r="E33">
-        <v>-17.8677438457541</v>
+        <v>-18.76809504795911</v>
       </c>
       <c r="F33">
-        <v>-2.178368675165604</v>
+        <v>-1.277196889701453</v>
       </c>
       <c r="G33">
-        <v>-0.55826592954084</v>
+        <v>-1.634473788823112</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.1879928419455969</v>
       </c>
       <c r="E34">
-        <v>-18.14415737070829</v>
+        <v>-18.54793875560221</v>
       </c>
       <c r="F34">
-        <v>-2.04016551441734</v>
+        <v>-1.371834552001685</v>
       </c>
       <c r="G34">
-        <v>-0.2299600251890395</v>
+        <v>-2.104886117692904</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.7741307075909228</v>
       </c>
       <c r="E35">
-        <v>-17.15018902534269</v>
+        <v>-17.60721620761881</v>
       </c>
       <c r="F35">
-        <v>-1.9734877370638</v>
+        <v>-1.610837600159607</v>
       </c>
       <c r="G35">
-        <v>-0.4806289462228185</v>
+        <v>-2.256094650816795</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.382535046583611</v>
       </c>
       <c r="E36">
-        <v>-16.81301696462759</v>
+        <v>-18.80429566917643</v>
       </c>
       <c r="F36">
-        <v>-1.834891930166609</v>
+        <v>-1.040568770887357</v>
       </c>
       <c r="G36">
-        <v>-0.01997497027081543</v>
+        <v>-2.252301558694076</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.967447164407611</v>
       </c>
       <c r="E37">
-        <v>-16.34695547670617</v>
+        <v>-17.82177077762822</v>
       </c>
       <c r="F37">
-        <v>-1.800091387207599</v>
+        <v>-1.225753617252798</v>
       </c>
       <c r="G37">
-        <v>-0.1303585447520951</v>
+        <v>-2.367216500148949</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.489796759942575</v>
       </c>
       <c r="E38">
-        <v>-16.14524818745652</v>
+        <v>-17.15168795023924</v>
       </c>
       <c r="F38">
-        <v>-1.616601380548286</v>
+        <v>-1.116281551503232</v>
       </c>
       <c r="G38">
-        <v>-0.6646726634920727</v>
+        <v>-2.336881606831883</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.923260386455322</v>
       </c>
       <c r="E39">
-        <v>-15.23877448839313</v>
+        <v>-17.52914531572657</v>
       </c>
       <c r="F39">
-        <v>-1.531957970962829</v>
+        <v>-1.062099696420922</v>
       </c>
       <c r="G39">
-        <v>0.2723949955619465</v>
+        <v>-2.005954006454086</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.252124206863296</v>
       </c>
       <c r="E40">
-        <v>-15.42378076550249</v>
+        <v>-16.55393390970076</v>
       </c>
       <c r="F40">
-        <v>-1.550915987343299</v>
+        <v>-0.9748361607404108</v>
       </c>
       <c r="G40">
-        <v>0.2602971316722739</v>
+        <v>-1.97455599735176</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.472026832457136</v>
       </c>
       <c r="E41">
-        <v>-14.57201103245176</v>
+        <v>-15.67302344641066</v>
       </c>
       <c r="F41">
-        <v>-1.532802905713685</v>
+        <v>-0.9172339766519415</v>
       </c>
       <c r="G41">
-        <v>0.005835118515776701</v>
+        <v>-1.099060460860721</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.589489128896466</v>
       </c>
       <c r="E42">
-        <v>-14.61072042826933</v>
+        <v>-15.09771705152821</v>
       </c>
       <c r="F42">
-        <v>-1.438919886117403</v>
+        <v>-1.176281030855403</v>
       </c>
       <c r="G42">
-        <v>0.4708465566987224</v>
+        <v>-2.457230251189197</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.619265769204677</v>
       </c>
       <c r="E43">
-        <v>-14.40838820960662</v>
+        <v>-14.82783811456708</v>
       </c>
       <c r="F43">
-        <v>-1.344444583828119</v>
+        <v>-1.206571941673573</v>
       </c>
       <c r="G43">
-        <v>0.5958184422332933</v>
+        <v>-1.187778129384987</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.579119664949412</v>
       </c>
       <c r="E44">
-        <v>-13.37936494694765</v>
+        <v>-14.14479932304215</v>
       </c>
       <c r="F44">
-        <v>-1.403170862482187</v>
+        <v>-1.060172085474608</v>
       </c>
       <c r="G44">
-        <v>0.5722658338795991</v>
+        <v>-1.418041133540579</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.487295333434577</v>
       </c>
       <c r="E45">
-        <v>-12.95837988929858</v>
+        <v>-14.44312613371945</v>
       </c>
       <c r="F45">
-        <v>-1.57365301581534</v>
+        <v>-0.9180623440547411</v>
       </c>
       <c r="G45">
-        <v>0.7664058698872646</v>
+        <v>-0.7917281247168909</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>3.360371973894513</v>
       </c>
       <c r="E46">
-        <v>-13.14767463129321</v>
+        <v>-13.50655619640109</v>
       </c>
       <c r="F46">
-        <v>-1.331048226190046</v>
+        <v>-0.8636982481438151</v>
       </c>
       <c r="G46">
-        <v>0.7211315748100464</v>
+        <v>-0.4700568503582876</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>3.210623037485969</v>
       </c>
       <c r="E47">
-        <v>-12.69061574969904</v>
+        <v>-13.02431447085026</v>
       </c>
       <c r="F47">
-        <v>-1.212007688570743</v>
+        <v>-0.6334568420053037</v>
       </c>
       <c r="G47">
-        <v>0.9871270817479917</v>
+        <v>-1.47978716084621</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.046634764271783</v>
       </c>
       <c r="E48">
-        <v>-11.1565906511267</v>
+        <v>-13.71785026512498</v>
       </c>
       <c r="F48">
-        <v>-1.503544969046806</v>
+        <v>-1.528182272340869</v>
       </c>
       <c r="G48">
-        <v>0.5809282587965331</v>
+        <v>-1.08210638906307</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>2.872705767314546</v>
       </c>
       <c r="E49">
-        <v>-12.24820195304568</v>
+        <v>-12.19997370486399</v>
       </c>
       <c r="F49">
-        <v>-1.419431714599142</v>
+        <v>-0.5987739272174912</v>
       </c>
       <c r="G49">
-        <v>0.8383007154762577</v>
+        <v>0.3917297424573914</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.689367252469162</v>
       </c>
       <c r="E50">
-        <v>-11.59001542687484</v>
+        <v>-11.62184154220075</v>
       </c>
       <c r="F50">
-        <v>-1.322781119510107</v>
+        <v>-1.045927479616067</v>
       </c>
       <c r="G50">
-        <v>0.6269539536108641</v>
+        <v>-0.03118362311787858</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>2.494923718579745</v>
       </c>
       <c r="E51">
-        <v>-10.86132961735259</v>
+        <v>-11.95010609454276</v>
       </c>
       <c r="F51">
-        <v>-1.102195163818626</v>
+        <v>-0.5954248378079728</v>
       </c>
       <c r="G51">
-        <v>0.6556744859206838</v>
+        <v>-0.3879705306056592</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.286563512552628</v>
       </c>
       <c r="E52">
-        <v>-10.15472011861773</v>
+        <v>-11.8323476564473</v>
       </c>
       <c r="F52">
-        <v>-1.190287066901937</v>
+        <v>-0.9517768973486809</v>
       </c>
       <c r="G52">
-        <v>1.133449875969869</v>
+        <v>-1.078303453275673</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>2.059720623499498</v>
       </c>
       <c r="E53">
-        <v>-9.607146098558243</v>
+        <v>-11.48035390030509</v>
       </c>
       <c r="F53">
-        <v>-1.437826441145708</v>
+        <v>-1.199196986686448</v>
       </c>
       <c r="G53">
-        <v>0.5648240233827785</v>
+        <v>-1.539141177635005</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.808036334071139</v>
       </c>
       <c r="E54">
-        <v>-9.180024958628781</v>
+        <v>-9.924800436300288</v>
       </c>
       <c r="F54">
-        <v>-1.268556189322851</v>
+        <v>-0.7652252447686211</v>
       </c>
       <c r="G54">
-        <v>-0.06382521519123462</v>
+        <v>-1.436625972453274</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.52982813995683</v>
       </c>
       <c r="E55">
-        <v>-9.999660640121085</v>
+        <v>-10.29484921831108</v>
       </c>
       <c r="F55">
-        <v>-0.9181360687535902</v>
+        <v>-1.048459798766425</v>
       </c>
       <c r="G55">
-        <v>0.03932326575146947</v>
+        <v>-1.383161748363682</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.22682982053197</v>
       </c>
       <c r="E56">
-        <v>-8.596014836703581</v>
+        <v>-9.418458172080641</v>
       </c>
       <c r="F56">
-        <v>-1.063468159370347</v>
+        <v>-0.4383216463974354</v>
       </c>
       <c r="G56">
-        <v>-0.2995448908001835</v>
+        <v>-1.576684914718172</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.9041980649486883</v>
       </c>
       <c r="E57">
-        <v>-8.460160616473472</v>
+        <v>-10.19012372840969</v>
       </c>
       <c r="F57">
-        <v>-0.76296131665677</v>
+        <v>-0.807215188416528</v>
       </c>
       <c r="G57">
-        <v>-0.7075155733937423</v>
+        <v>-1.681621661410773</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.5680261780248836</v>
       </c>
       <c r="E58">
-        <v>-7.435145053311293</v>
+        <v>-8.934631480627132</v>
       </c>
       <c r="F58">
-        <v>-0.7013473492365427</v>
+        <v>-0.891012834883726</v>
       </c>
       <c r="G58">
-        <v>-1.228494807716136</v>
+        <v>-1.718197438133904</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.2267933875130719</v>
       </c>
       <c r="E59">
-        <v>-7.85766526364896</v>
+        <v>-9.004786599953961</v>
       </c>
       <c r="F59">
-        <v>-0.75696642176271</v>
+        <v>-0.04500286313939649</v>
       </c>
       <c r="G59">
-        <v>-0.6063095756142295</v>
+        <v>-2.498563799173521</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.1110592055560269</v>
       </c>
       <c r="E60">
-        <v>-7.825110064007818</v>
+        <v>-8.250179805211804</v>
       </c>
       <c r="F60">
-        <v>-0.7516880646720715</v>
+        <v>-0.5540222066486507</v>
       </c>
       <c r="G60">
-        <v>-1.260722965873002</v>
+        <v>-2.739884519984443</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.4365234837413889</v>
       </c>
       <c r="E61">
-        <v>-6.933340320047334</v>
+        <v>-7.422161918331303</v>
       </c>
       <c r="F61">
-        <v>-0.5054003535739309</v>
+        <v>-0.3292513388382273</v>
       </c>
       <c r="G61">
-        <v>-1.31262204727874</v>
+        <v>-2.080670702584202</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.7393364800238912</v>
       </c>
       <c r="E62">
-        <v>-7.114787216586669</v>
+        <v>-8.168966152358244</v>
       </c>
       <c r="F62">
-        <v>-0.4505781704892569</v>
+        <v>-0.8068250273698094</v>
       </c>
       <c r="G62">
-        <v>-2.058492926063915</v>
+        <v>-2.83385542422538</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.009514921468458</v>
       </c>
       <c r="E63">
-        <v>-6.641856033595616</v>
+        <v>-7.533118588467241</v>
       </c>
       <c r="F63">
-        <v>-0.6516742979276704</v>
+        <v>-0.3775791214849532</v>
       </c>
       <c r="G63">
-        <v>-2.153733663048357</v>
+        <v>-3.1252902419137</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.2413345938754</v>
       </c>
       <c r="E64">
-        <v>-6.542609997243512</v>
+        <v>-7.634583577083103</v>
       </c>
       <c r="F64">
-        <v>-0.7511744768823359</v>
+        <v>-0.7008412167534323</v>
       </c>
       <c r="G64">
-        <v>-2.209150213965819</v>
+        <v>-4.826068781371595</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.434298249239184</v>
       </c>
       <c r="E65">
-        <v>-6.183805416193766</v>
+        <v>-7.033469408830933</v>
       </c>
       <c r="F65">
-        <v>-0.5733090848880316</v>
+        <v>-0.1728547448222778</v>
       </c>
       <c r="G65">
-        <v>-2.198535462221015</v>
+        <v>-3.836462202707748</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.586703626198219</v>
       </c>
       <c r="E66">
-        <v>-5.332230407525364</v>
+        <v>-8.310702860324319</v>
       </c>
       <c r="F66">
-        <v>-0.8995334219889217</v>
+        <v>-0.2530514781895064</v>
       </c>
       <c r="G66">
-        <v>-2.51630208292388</v>
+        <v>-3.514298745115228</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.698937342550263</v>
       </c>
       <c r="E67">
-        <v>-5.980667129157689</v>
+        <v>-7.864865537321156</v>
       </c>
       <c r="F67">
-        <v>-0.7474667043874053</v>
+        <v>-0.06654704255140603</v>
       </c>
       <c r="G67">
-        <v>-2.776496390144727</v>
+        <v>-4.436344971870109</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.774142169553019</v>
       </c>
       <c r="E68">
-        <v>-5.7546736338049</v>
+        <v>-7.121022925295232</v>
       </c>
       <c r="F68">
-        <v>-0.8594669474503152</v>
+        <v>-0.5948184728691236</v>
       </c>
       <c r="G68">
-        <v>-2.658972877550095</v>
+        <v>-4.709838070071386</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.818530795015995</v>
       </c>
       <c r="E69">
-        <v>-5.429434102100008</v>
+        <v>-7.128875299224532</v>
       </c>
       <c r="F69">
-        <v>-0.8751421438134902</v>
+        <v>-0.5873474272632748</v>
       </c>
       <c r="G69">
-        <v>-3.403317988310129</v>
+        <v>-4.742555130240609</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.839648629549774</v>
       </c>
       <c r="E70">
-        <v>-6.004373690587844</v>
+        <v>-6.869112973196545</v>
       </c>
       <c r="F70">
-        <v>-0.9735165714677512</v>
+        <v>-0.5950860355402278</v>
       </c>
       <c r="G70">
-        <v>-3.002195215111132</v>
+        <v>-4.172666007353132</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.846905267676121</v>
       </c>
       <c r="E71">
-        <v>-5.694884191481629</v>
+        <v>-6.771882107777855</v>
       </c>
       <c r="F71">
-        <v>-0.7080877747931223</v>
+        <v>-0.64504901544008</v>
       </c>
       <c r="G71">
-        <v>-3.357505572897162</v>
+        <v>-4.536917693888649</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.852525194795799</v>
       </c>
       <c r="E72">
-        <v>-6.167960285640928</v>
+        <v>-6.662288508318224</v>
       </c>
       <c r="F72">
-        <v>-1.05064503197501</v>
+        <v>-0.1342751897716964</v>
       </c>
       <c r="G72">
-        <v>-3.68724537107044</v>
+        <v>-4.611801732318296</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.869906801610091</v>
       </c>
       <c r="E73">
-        <v>-5.632087842417264</v>
+        <v>-6.995067949245888</v>
       </c>
       <c r="F73">
-        <v>-1.19237123928738</v>
+        <v>-0.788031856102497</v>
       </c>
       <c r="G73">
-        <v>-2.71011727799716</v>
+        <v>-5.142171822743821</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.911071920593493</v>
       </c>
       <c r="E74">
-        <v>-5.671721046932395</v>
+        <v>-7.495446213197432</v>
       </c>
       <c r="F74">
-        <v>-1.060600351421855</v>
+        <v>-0.8417713629917122</v>
       </c>
       <c r="G74">
-        <v>-3.151018300161306</v>
+        <v>-4.700158466471024</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.984467587558875</v>
       </c>
       <c r="E75">
-        <v>-6.848934093018365</v>
+        <v>-6.521919399502466</v>
       </c>
       <c r="F75">
-        <v>-1.284339901815793</v>
+        <v>-0.9766395165763053</v>
       </c>
       <c r="G75">
-        <v>-3.041628935812538</v>
+        <v>-4.276897291410452</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.096829702129154</v>
       </c>
       <c r="E76">
-        <v>-6.59453348021546</v>
+        <v>-7.546948548086667</v>
       </c>
       <c r="F76">
-        <v>-1.394268398004301</v>
+        <v>-0.8706921541256513</v>
       </c>
       <c r="G76">
-        <v>-2.775574366886523</v>
+        <v>-4.176285194733199</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.251437525206363</v>
       </c>
       <c r="E77">
-        <v>-7.55946072176986</v>
+        <v>-8.07088846230012</v>
       </c>
       <c r="F77">
-        <v>-1.443661461131027</v>
+        <v>-1.110097788841334</v>
       </c>
       <c r="G77">
-        <v>-2.645214715551344</v>
+        <v>-4.594985471826142</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.448147339143885</v>
       </c>
       <c r="E78">
-        <v>-7.7415597185663</v>
+        <v>-8.185952458361015</v>
       </c>
       <c r="F78">
-        <v>-1.387238043856742</v>
+        <v>-1.294987736411378</v>
       </c>
       <c r="G78">
-        <v>-2.689701517454295</v>
+        <v>-3.965361710448974</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.681756533103051</v>
       </c>
       <c r="E79">
-        <v>-7.227061672658841</v>
+        <v>-8.881286056816776</v>
       </c>
       <c r="F79">
-        <v>-1.585400922321842</v>
+        <v>-1.337105248639316</v>
       </c>
       <c r="G79">
-        <v>-2.571502073218418</v>
+        <v>-3.968528089253838</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.94729297761488</v>
       </c>
       <c r="E80">
-        <v>-8.143104037300439</v>
+        <v>-10.43731501059239</v>
       </c>
       <c r="F80">
-        <v>-1.756666711218043</v>
+        <v>-0.8532053182525537</v>
       </c>
       <c r="G80">
-        <v>-2.112439489722746</v>
+        <v>-4.032544721878605</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.236096062597902</v>
       </c>
       <c r="E81">
-        <v>-8.439569645160594</v>
+        <v>-10.2747880784571</v>
       </c>
       <c r="F81">
-        <v>-1.425434064799827</v>
+        <v>-1.450695957115601</v>
       </c>
       <c r="G81">
-        <v>-2.076296834245462</v>
+        <v>-3.886251458650762</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.53664610492995</v>
       </c>
       <c r="E82">
-        <v>-9.44221454672488</v>
+        <v>-11.17287504365828</v>
       </c>
       <c r="F82">
-        <v>-1.593273726118049</v>
+        <v>-1.234939383382442</v>
       </c>
       <c r="G82">
-        <v>-2.206686016574676</v>
+        <v>-3.901276172171459</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.836066922327078</v>
       </c>
       <c r="E83">
-        <v>-10.18698549592238</v>
+        <v>-11.80443867113803</v>
       </c>
       <c r="F83">
-        <v>-1.74830682738899</v>
+        <v>-1.263221503248822</v>
       </c>
       <c r="G83">
-        <v>-2.06703066456159</v>
+        <v>-3.978115818650536</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.122973842872917</v>
       </c>
       <c r="E84">
-        <v>-11.6643820270288</v>
+        <v>-12.51212594668672</v>
       </c>
       <c r="F84">
-        <v>-2.00360137725777</v>
+        <v>-1.364163041484359</v>
       </c>
       <c r="G84">
-        <v>-2.077340262701366</v>
+        <v>-3.604079529424754</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.385822294498637</v>
       </c>
       <c r="E85">
-        <v>-13.12177175996934</v>
+        <v>-13.45163033516205</v>
       </c>
       <c r="F85">
-        <v>-2.29307519453346</v>
+        <v>-1.509780918855081</v>
       </c>
       <c r="G85">
-        <v>-2.305821563550179</v>
+        <v>-4.67820053179522</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.613543448299818</v>
       </c>
       <c r="E86">
-        <v>-13.78898353483746</v>
+        <v>-15.90441488278059</v>
       </c>
       <c r="F86">
-        <v>-2.294504128303289</v>
+        <v>-1.850884391245056</v>
       </c>
       <c r="G86">
-        <v>-1.763402827558374</v>
+        <v>-3.612814141215996</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.800245756430749</v>
       </c>
       <c r="E87">
-        <v>-14.44231100839808</v>
+        <v>-15.98404809820548</v>
       </c>
       <c r="F87">
-        <v>-2.419827004305424</v>
+        <v>-1.479992827050411</v>
       </c>
       <c r="G87">
-        <v>-1.502050249127042</v>
+        <v>-2.949876137345786</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.946427465952745</v>
       </c>
       <c r="E88">
-        <v>-17.06926519482563</v>
+        <v>-17.06213737673755</v>
       </c>
       <c r="F88">
-        <v>-2.564837688369894</v>
+        <v>-1.738920596347869</v>
       </c>
       <c r="G88">
-        <v>-1.185645335371348</v>
+        <v>-2.424231005965861</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.05953401082818</v>
       </c>
       <c r="E89">
-        <v>-17.92732497827301</v>
+        <v>-18.75733539371689</v>
       </c>
       <c r="F89">
-        <v>-2.939520690167152</v>
+        <v>-2.005001318168501</v>
       </c>
       <c r="G89">
-        <v>-1.030108871010549</v>
+        <v>-2.895844261926409</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.151109249950939</v>
       </c>
       <c r="E90">
-        <v>-19.20030166419919</v>
+        <v>-20.5920285240285</v>
       </c>
       <c r="F90">
-        <v>-2.707304456140367</v>
+        <v>-2.072884370093115</v>
       </c>
       <c r="G90">
-        <v>-1.52729596780541</v>
+        <v>-3.147130052613364</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.238831321192394</v>
       </c>
       <c r="E91">
-        <v>-20.85169122362832</v>
+        <v>-21.20220869724403</v>
       </c>
       <c r="F91">
-        <v>-2.968132500259847</v>
+        <v>-2.26310072006316</v>
       </c>
       <c r="G91">
-        <v>-1.26818446369918</v>
+        <v>-3.300228569355495</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.3392064978987</v>
       </c>
       <c r="E92">
-        <v>-23.46922618411992</v>
+        <v>-24.03715569484388</v>
       </c>
       <c r="F92">
-        <v>-3.042486758335131</v>
+        <v>-2.568698708834342</v>
       </c>
       <c r="G92">
-        <v>-0.738450930256187</v>
+        <v>-2.972739689171996</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.46603496298065</v>
       </c>
       <c r="E93">
-        <v>-25.17498460248514</v>
+        <v>-25.09320036190662</v>
       </c>
       <c r="F93">
-        <v>-3.250514664200171</v>
+        <v>-2.75230551529745</v>
       </c>
       <c r="G93">
-        <v>-0.8605878403633977</v>
+        <v>-2.547775560122073</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.627359882135825</v>
       </c>
       <c r="E94">
-        <v>-27.45229983925448</v>
+        <v>-27.82672765563068</v>
       </c>
       <c r="F94">
-        <v>-3.393543893437144</v>
+        <v>-2.960296144629364</v>
       </c>
       <c r="G94">
-        <v>-0.9007171800354066</v>
+        <v>-2.720889528376817</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.831534201818705</v>
       </c>
       <c r="E95">
-        <v>-29.55019014312889</v>
+        <v>-30.15010653000604</v>
       </c>
       <c r="F95">
-        <v>-3.360929412054122</v>
+        <v>-2.943907723932378</v>
       </c>
       <c r="G95">
-        <v>-1.073099435882394</v>
+        <v>-3.582685964857174</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.085338864379002</v>
       </c>
       <c r="E96">
-        <v>-32.52290464122709</v>
+        <v>-33.31846695489462</v>
       </c>
       <c r="F96">
-        <v>-3.578353489369117</v>
+        <v>-3.101717512737504</v>
       </c>
       <c r="G96">
-        <v>-1.78002549597852</v>
+        <v>-2.66467892184197</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.383922446698473</v>
       </c>
       <c r="E97">
-        <v>-34.75877528387823</v>
+        <v>-36.23426306319042</v>
       </c>
       <c r="F97">
-        <v>-3.9776033832312</v>
+        <v>-3.402725517729774</v>
       </c>
       <c r="G97">
-        <v>-1.312280800236557</v>
+        <v>-2.763620876745466</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.728646248159344</v>
       </c>
       <c r="E98">
-        <v>-37.42613025116521</v>
+        <v>-38.20252353435827</v>
       </c>
       <c r="F98">
-        <v>-3.870590740300546</v>
+        <v>-3.70332679432727</v>
       </c>
       <c r="G98">
-        <v>-2.288703430674556</v>
+        <v>-3.984379670607515</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.098415725253711</v>
       </c>
       <c r="E99">
-        <v>-39.63634029585188</v>
+        <v>-41.34110697840942</v>
       </c>
       <c r="F99">
-        <v>-4.152538839721803</v>
+        <v>-3.468623801357281</v>
       </c>
       <c r="G99">
-        <v>-1.826441656158425</v>
+        <v>-3.583089555108986</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.502594385160386</v>
       </c>
       <c r="E100">
-        <v>-42.5337892917056</v>
+        <v>-42.63104053525732</v>
       </c>
       <c r="F100">
-        <v>-4.483672910419085</v>
+        <v>-3.94984230646118</v>
       </c>
       <c r="G100">
-        <v>-2.492359009204612</v>
+        <v>-4.679808330359347</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.897070830019929</v>
       </c>
       <c r="E101">
-        <v>-44.74393140928215</v>
+        <v>-45.44539203307028</v>
       </c>
       <c r="F101">
-        <v>-4.341325427554615</v>
+        <v>-3.987621658600657</v>
       </c>
       <c r="G101">
-        <v>-2.770327693612971</v>
+        <v>-4.362369831812428</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.319392008773562</v>
       </c>
       <c r="E102">
-        <v>-48.64276639092602</v>
+        <v>-47.61303215784785</v>
       </c>
       <c r="F102">
-        <v>-4.595873618393473</v>
+        <v>-4.044379736305674</v>
       </c>
       <c r="G102">
-        <v>-2.602483367182695</v>
+        <v>-4.095944484850195</v>
       </c>
     </row>
   </sheetData>
